--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/验收策略.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/验收策略.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,300 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>到货</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>设备到货清点</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>型号/数量与 BOQ 一致，外观无损</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>到货签收</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>到货验收单</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>到货</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>整机柜 ST 测试</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GPU 数量与 BOQ 一致，误码率 ≤ 1e-12</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>部署调测完成</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>验收测试报告</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RDMA 全互联压测</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>400G 带宽达标，时延 p99 ≤ 2μs</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>集群联调完成</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>网络测试报告</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>维保</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>维保服务启动</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>维保策略与 SLA 合同一致</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>维保生效</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>维保确认函</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>培训</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AI 使能培训</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>参训人数 ≥ 合同，考核通过</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>培训完成</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>培训签到表</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>整体性能基线</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RTO ≤ 5s / p99 ≤ 30ms</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>整体压测完成</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>性能基线报告</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>终验</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>客户签收移交</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>文档齐套，客户代表签字</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>客户验收</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>移交确认函</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>终验</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/验收策略.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/验收策略.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,6 +1088,300 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>到货</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>设备到货清点</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>型号/数量与 BOQ 一致，外观无损</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>到货签收</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>到货验收单</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>到货</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>整机柜 ST 测试</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GPU 数量与 BOQ 一致，误码率 ≤ 1e-12</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>部署调测完成</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>验收测试报告</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RDMA 全互联压测</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>400G 带宽达标，时延 p99 ≤ 2μs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>集群联调完成</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>网络测试报告</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>维保</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>维保服务启动</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>维保策略与 SLA 合同一致</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>维保生效</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>维保确认函</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>培训</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AI 使能培训</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>参训人数 ≥ 合同，考核通过</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>培训完成</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>培训签到表</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>整体性能基线</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RTO ≤ 5s / p99 ≤ 30ms</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>整体压测完成</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>性能基线报告</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>终验</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>客户签收移交</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>文档齐套，客户代表签字</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>客户验收</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>移交确认函</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>终验</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/验收策略.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/验收策略.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1382,6 +1382,300 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>到货</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>设备到货清点</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>型号/数量与 BOQ 一致，外观无损</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>到货签收</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>到货验收单</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>到货</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>整机柜 ST 测试</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GPU 数量与 BOQ 一致，误码率 ≤ 1e-12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>部署调测完成</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>验收测试报告</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RDMA 全互联压测</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>400G 带宽达标，时延 p99 ≤ 2μs</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>集群联调完成</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>网络测试报告</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>维保</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>维保服务启动</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>维保策略与 SLA 合同一致</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>维保生效</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>维保确认函</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>培训</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AI 使能培训</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>参训人数 ≥ 合同，考核通过</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>培训完成</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>培训签到表</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>整体性能基线</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RTO ≤ 5s / p99 ≤ 30ms</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>整体压测完成</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>性能基线报告</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>终验</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>客户签收移交</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>文档齐套，客户代表签字</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>客户验收</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>移交确认函</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>终验</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
